--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_43.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_43.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment?</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.3360206941631326</v>
+        <v>-0.07727365037406379</v>
       </c>
       <c r="C2">
-        <v>-0.4335938476611979</v>
+        <v>-0.316911691719832</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.09960590923614472</v>
+        <v>-0.02932670921366437</v>
       </c>
       <c r="C3">
-        <v>0.8043267083903823</v>
+        <v>-1.888929019851519</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-1.129043883030825</v>
+        <v>-0.1176202214673923</v>
       </c>
       <c r="C4">
-        <v>-2.145467520488612</v>
+        <v>0.5615049044043323</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3001384472333979</v>
+        <v>-0.5234160702475145</v>
       </c>
       <c r="C5">
-        <v>-0.7052822588642065</v>
+        <v>-0.6046197592506291</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.611782419072135</v>
+        <v>-0.255420096028562</v>
       </c>
       <c r="C6">
-        <v>-0.5481774093418085</v>
+        <v>-0.4005750074909157</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.8987656496179042</v>
+        <v>-1.322326802296849</v>
       </c>
       <c r="C7">
-        <v>0.312326541638274</v>
+        <v>-1.672854881363376</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>2.351248219248314</v>
+        <v>0.4374813027188693</v>
       </c>
       <c r="C8">
-        <v>-1.328070273739066</v>
+        <v>1.269868763848988</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.4796334509993948</v>
+        <v>-0.5518305597646864</v>
       </c>
       <c r="C9">
-        <v>2.115637385896699</v>
+        <v>-0.8876371626346682</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.9104919358915103</v>
+        <v>-0.147584901463064</v>
       </c>
       <c r="C10">
-        <v>0.1125570973026659</v>
+        <v>0.1558916165938203</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.5863368040219993</v>
+        <v>-0.8184259450030104</v>
       </c>
       <c r="C11">
-        <v>0.6597932377842717</v>
+        <v>1.085614501899416</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.1087361022569781</v>
+        <v>0.456763536516321</v>
       </c>
       <c r="C12">
-        <v>-0.1043603183481672</v>
+        <v>0.4413323208938846</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.04030813138424945</v>
+        <v>0.1956139673152142</v>
       </c>
       <c r="C13">
-        <v>1.125296681680159</v>
+        <v>1.236890148817925</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.779029622631675</v>
+        <v>-0.8963105291978306</v>
       </c>
       <c r="C14">
-        <v>-0.9009132224877011</v>
+        <v>-0.3080839935751988</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.4634217090054071</v>
+        <v>-0.4875782217712514</v>
       </c>
       <c r="C15">
-        <v>0.74314351077117</v>
+        <v>-0.636731879940915</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.7827299176824866</v>
+        <v>0.9084199317466264</v>
       </c>
       <c r="C16">
-        <v>-0.6512237727898578</v>
+        <v>0.6855614725592845</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.4605723641952435</v>
+        <v>0.4144764276968118</v>
       </c>
       <c r="C17">
-        <v>0.9058240795217367</v>
+        <v>-0.02758355806274149</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.4295955633565527</v>
+        <v>0.4149295586961999</v>
       </c>
       <c r="C18">
-        <v>-0.5559170080416974</v>
+        <v>0.6706693865392576</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.679322914045126</v>
+        <v>-1.627328610745009</v>
       </c>
       <c r="C19">
-        <v>-1.053121107065177</v>
+        <v>-0.8385579369243494</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.140639690726596</v>
+        <v>1.648312929342953</v>
       </c>
       <c r="C20">
-        <v>0.5001020932762665</v>
+        <v>-0.2353977527748303</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.17121174759588</v>
+        <v>-0.655681857493722</v>
       </c>
       <c r="C21">
-        <v>-0.5220909478148735</v>
+        <v>0.2292118880243664</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.451353447482255</v>
+        <v>-0.008770805161164645</v>
       </c>
       <c r="C22">
-        <v>-0.5044949375182523</v>
+        <v>-0.9937094610026608</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.9964975474292483</v>
+        <v>0.7350429373504693</v>
       </c>
       <c r="C23">
-        <v>-0.008609857742330831</v>
+        <v>0.2965337572544618</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-2.471061318183457</v>
+        <v>0.7427556402919611</v>
       </c>
       <c r="C24">
-        <v>0.2799387853615697</v>
+        <v>0.5521295325514808</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.3258002313602248</v>
+        <v>0.8364317926022452</v>
       </c>
       <c r="C25">
-        <v>1.068608323773395</v>
+        <v>-0.8194956105965192</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.929950905981318</v>
+        <v>0.2123155261299</v>
       </c>
       <c r="C26">
-        <v>0.1591929469955468</v>
+        <v>1.49564187962209</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.9835512400821802</v>
+        <v>-0.8961685113086226</v>
       </c>
       <c r="C27">
-        <v>-0.1918378757331517</v>
+        <v>-0.365752799832344</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.4651918092202094</v>
+        <v>0.5427776049708732</v>
       </c>
       <c r="C28">
-        <v>-0.304773104935586</v>
+        <v>-0.05456365969977012</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.7909353300575149</v>
+        <v>-0.6154029641617249</v>
       </c>
       <c r="C29">
-        <v>1.157226688082629</v>
+        <v>1.561312906031953</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.08304154775313986</v>
+        <v>-0.2457352282787154</v>
       </c>
       <c r="C30">
-        <v>1.469069522351789</v>
+        <v>-1.193681440311574</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.3614366813593576</v>
+        <v>0.5231643160430485</v>
       </c>
       <c r="C31">
-        <v>0.1667352362301309</v>
+        <v>0.2232368223462382</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-1.280004406440342</v>
+        <v>1.025372889543163</v>
       </c>
       <c r="C32">
-        <v>0.3965426434132032</v>
+        <v>0.7072747482856312</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.403512023163124</v>
+        <v>0.5620641368379793</v>
       </c>
       <c r="C33">
-        <v>-1.030842174392274</v>
+        <v>0.06967904690758039</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.09924963163755184</v>
+        <v>0.3774289977496973</v>
       </c>
       <c r="C34">
-        <v>-0.05191144578838568</v>
+        <v>-0.344068129414983</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.2800897753742481</v>
+        <v>-0.1206658501397483</v>
       </c>
       <c r="C35">
-        <v>-2.219082742015716</v>
+        <v>-0.7069620012738539</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.5916608362629201</v>
+        <v>1.15002662706341</v>
       </c>
       <c r="C36">
-        <v>2.597551202833595</v>
+        <v>0.6616387743414675</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.7550686679664472</v>
+        <v>0.9948990100080642</v>
       </c>
       <c r="C37">
-        <v>-1.910006598054739</v>
+        <v>0.2093215923321228</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.001907999046477</v>
+        <v>0.6043563872259482</v>
       </c>
       <c r="C38">
-        <v>-0.9232534231992509</v>
+        <v>-0.455893148363997</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.548861542282523</v>
+        <v>-0.1698441529363924</v>
       </c>
       <c r="C39">
-        <v>-0.2926409595924898</v>
+        <v>-1.186426108880283</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.019761898980718</v>
+        <v>-0.01496028163589033</v>
       </c>
       <c r="C40">
-        <v>-0.8830602443287586</v>
+        <v>-2.156641392790169</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.5738250098178059</v>
+        <v>1.128244760064929</v>
       </c>
       <c r="C41">
-        <v>-0.1102876100132017</v>
+        <v>0.223953342432484</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>1.031251742604386</v>
+        <v>-0.5979644329178504</v>
       </c>
       <c r="C42">
-        <v>-1.111149166539274</v>
+        <v>-1.464219949030552</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.2852054528345327</v>
+        <v>1.036280034904291</v>
       </c>
       <c r="C43">
-        <v>-0.6746474764062664</v>
+        <v>-0.3120836825030017</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.3778623882972764</v>
+        <v>1.39273687014252</v>
       </c>
       <c r="C44">
-        <v>0.3310494150065957</v>
+        <v>0.4154165487383478</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.8819917426470602</v>
+        <v>-0.8770750326559932</v>
       </c>
       <c r="C45">
-        <v>-0.3740761286250942</v>
+        <v>0.3189696747129793</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.855345144678754</v>
+        <v>0.7624518074793035</v>
       </c>
       <c r="C46">
-        <v>-2.376874502839876</v>
+        <v>-0.5825083375407328</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.085205173128293</v>
+        <v>-0.3857269438056046</v>
       </c>
       <c r="C47">
-        <v>-1.146124590596211</v>
+        <v>-1.009091003242704</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.6727827575850978</v>
+        <v>0.3102827856569981</v>
       </c>
       <c r="C48">
-        <v>-0.1125129068206395</v>
+        <v>-0.991830160352574</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.9740241164269728</v>
+        <v>2.00026904428125</v>
       </c>
       <c r="C49">
-        <v>1.070065628016877</v>
+        <v>-1.235820648650297</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.829230974049388</v>
+        <v>-0.8386887706286432</v>
       </c>
       <c r="C50">
-        <v>-0.01983314697656061</v>
+        <v>-1.812637632340019</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.8974877102925316</v>
+        <v>1.468482172926802</v>
       </c>
       <c r="C51">
-        <v>-0.1019147844887569</v>
+        <v>0.6816497433910951</v>
       </c>
     </row>
   </sheetData>
